--- a/Zagentexecution/incidents/xml_payment_structured_address/sepa_ct_unes_test_cases.xlsx
+++ b/Zagentexecution/incidents/xml_payment_structured_address/sepa_ct_unes_test_cases.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,7 +48,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="000F172A"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -58,13 +58,25 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001f2937"/>
+      <color rgb="0015803D"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00475569"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001f2937"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -87,14 +99,19 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0015803D"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="0015803D"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -127,14 +144,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="001E3A4A"/>
+        <bgColor rgb="001E3A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A4A"/>
-        <bgColor rgb="001E3A4A"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -176,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -202,28 +219,38 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -591,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -617,157 +644,145 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>📋 How to use this workbook</t>
+          <t>🔢 RECOMMENDED TEST EXECUTION ORDER</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1. Open one of the 3 case tabs (Case_1_Standard_Vendor / Case_2_Payroll / Case_3_Cross_Border_ES)</t>
+          <t>Run the 3 cases in this order. Each case = ~10-15 min (V000 + V001 + diff). Total time = ~30-45 min for the full SEPA tree validation.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2. In SAP: tx DMEE → enter Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
-        </is>
-      </c>
+      <c r="A6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>3. In the popup, choose 'Active version' for V000 testing or 'Maintenance version' for V001 testing</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>4. From the menu: Tree → Test (or button on toolbar) — opens the 'DMEE Test Data' screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>STEP 1 — Run Case 1 (Standard Vendor) FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Reason: highest-volume scenario (118,678 payments / 18.4% volume) — establishes baseline V000 known-good output and the V001 reference for diff. If something fails here, no point running Cases 2-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>5. Copy the row from each table in the case tab into the matching SAP grid (FPAYHX → FPAYH → FPAYP)</t>
+          <t xml:space="preserve">   1.1 — Open tab 'Case_1_Standard_Vendor' in this workbook</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Skip the 'Row' column from this Excel — it is just a counter for the worksheet</t>
+          <t xml:space="preserve">   1.2 — Follow the 15-step EXECUTION ORDER section at the top of that tab</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Keep 'No. FPAYHX' = 1 and 'No. FPAYH' = 1 for a single-payment test</t>
+          <t xml:space="preserve">   1.3 — Save outputs as case_1_V000.xml + case_1_V001.xml + diff observations</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>6. For Cdtr address to render: expand the FPAYHX grid layout to add Z-fields (ZLISO, ZPFST, ZPLOR, ZSTRA, ZBSTR…) — see each case's Z-FIELDS section</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>7. Click the Test/Run button → SAP engine produces the XML output</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>8. Inspect the XML against the 'Expected XML output observations' section in each case tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>STEP 2 — Run Case 2 (Payroll) SECOND</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Reason: second-highest-volume scenario (103,126 payments / 16% volume) and tests Doc cat=03 (Payroll) which differs from Case 1's Doc cat=01. Only point of variation: Doc cat. Validates the SEPA tree handles both invoice and payroll categories without format break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>9. To compare V000 vs V001 for the same case: re-open tx DMEE, this time pick Maintenance version, paste the same inputs, run, and diff XML outputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>📊 The 3 cases — coverage rationale</t>
+          <t xml:space="preserve">   2.1 — Open tab 'Case_2_Payroll'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2.2 — Follow the EXECUTION ORDER (same 15 steps, different values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2.3 — Save outputs as case_2_V000.xml + case_2_V001.xml</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Case 1 — Standard SEPA vendor payment (FR vendor, EUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Scenario #1 — 118,678 payments — 18.4% volume — Doc cat=01 (FI vendor invoice)</t>
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>STEP 3 — Run Case 3 (Cross-border ES) THIRD</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The most common scenario. Validates baseline V000 SEPA output and provides the V001 reference for diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Case 2 — SEPA Payroll (employee, EUR)</t>
+          <t xml:space="preserve">   Reason: tests SEPA-zone non-FR creditor — surfaces if the tree falls back to Dbtr-side country when Cdtr country is non-FR. This is the highest-information case for V001 design verification because it exercises Z-fields with non-FR data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   3.1 — Open tab 'Case_3_Cross_Border_ES'</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Scenario #2 — 103,126 payments — 16% volume — Doc cat=03 (Payroll info)</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   3.2 — Follow the EXECUTION ORDER</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Same tree, different document category. Validates that Doc cat=03 routes through the same SEPA chain without breaking format.</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   3.3 — Save outputs as case_3_V000.xml + case_3_V001.xml</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Case 3 — SEPA cross-border to ES vendor (Spanish vendor, EUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SEPA-zone non-FR creditor — Doc cat=01 (FI vendor invoice)</t>
+      <c r="A24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>STEP 4 — Consolidate findings</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Tests that non-FR Cdtr country is correctly emitted (Cdtr/PstlAdr/Ctry=ES). Surfaces if the tree falls back to Dbtr country.</t>
+          <t xml:space="preserve">   Compile the 6 XML outputs (3 cases × 2 versions). Note any unexpected behaviors per case. Hand back to project agent for diff analysis vs Python simulator predictions and finding capture in the brain.</t>
         </is>
       </c>
     </row>
@@ -777,35 +792,35 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>⚠ Known SEPA tree behaviors (from initial V000 test session 2026-05-01)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
+          <t>📋 General workbook navigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Amount × 100 at output: Amount=1500.00 in FPAYH produces CtrlSum=150000.00 in XML. Expected SEPA tree CV_RULE — production-correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
+          <t>Each case tab is self-contained — has the EXECUTION ORDER (15 steps) at the top + the 3 tables to copy + the Z-fields hint + expected XML observations + V001 testing reminder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • InitgPty/Nm = SOG01 (HBKID): bound to FPAYHX-Issuer field, not to UNESCO name. Flag for review with N_MENARD if business intent is 'UNESCO' rather than HBKID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
+          <t>Skip the 'Row' column from each table in the Excel — it is just a counter for the worksheet, not a SAP field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • UltmtCdtr/Nm bound to FPAYP-NAME1: when FPAYP 'Name' is populated, it appears as UltmtCdtr/Nm in the output XML.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
+          <t>Keep 'No. FPAYHX' = 1 and 'No. FPAYH' = 1 for a single-payment test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Cdtr/PstlAdr binding requires Z-fields (ZLISO/ZPFST/ZPLOR): hidden by default in FPAYHX layout. Without them populated, Cdtr address comes out empty or falls back to Dbtr-side fields.</t>
+          <t>For Cdtr address to render: expand the FPAYHX grid layout to add Z-fields (ZLISO, ZPFST, ZPLOR, ZSTRA, ZBSTR…) — see each case's Z-FIELDS section.</t>
         </is>
       </c>
     </row>
@@ -813,68 +828,188 @@
       <c r="A33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>🧪 What this enables (Layer 3 of the 4-layer testing methodology)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   This workbook delivers Layer 3 (DMEE Test Data with F110-history-replay-equivalent inputs) for the SEPA tree without requiring F110 execution.</t>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>📊 The 3 cases — coverage rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Case 1 — Standard SEPA vendor payment (FR vendor, EUR)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Layer 1 (Python simulator) = already done — 794 cases × 3 schemas = 2,382 PASS (claim 105)</t>
+          <t xml:space="preserve">   Scenario #1 — 118,678 payments — 18.4% volume — Doc cat=01 (FI vendor invoice)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Layer 2 (DMEE Test Data hand-crafted) = these 3 cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Layer 3 (DMEE Test Data F110-history replay) = next iteration — pull actual REGUH/REGUP rows for top-15 scenarios</t>
+          <t xml:space="preserve">   The most common scenario. Validates baseline V000 SEPA output and provides the V001 reference for diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Case 2 — SEPA Payroll (employee, EUR)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Layer 4 (D01 F110 integration) = Phase 3 final integration test</t>
+          <t xml:space="preserve">   Scenario #2 — 103,126 payments — 16% volume — Doc cat=03 (Payroll info)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Same tree, different document category. Validates that Doc cat=03 routes through the same SEPA chain without breaking format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Case 3 — SEPA cross-border to ES vendor (Spanish vendor, EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SEPA-zone non-FR creditor — Doc cat=01 (FI vendor invoice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tests that non-FR Cdtr country is correctly emitted (Cdtr/PstlAdr/Ctry=ES). Surfaces if the tree falls back to Dbtr country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>⚠ Known SEPA tree behaviors (from initial V000 test session 2026-05-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Amount × 100 at output: Amount=1500.00 in FPAYH produces CtrlSum=150000.00 in XML. Expected SEPA tree CV_RULE — production-correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • InitgPty/Nm = SOG01 (HBKID): bound to FPAYHX-Issuer field, not to UNESCO name. Flag for review with N_MENARD if business intent is 'UNESCO' rather than HBKID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • UltmtCdtr/Nm bound to FPAYP-NAME1: when FPAYP 'Name' is populated, it appears as UltmtCdtr/Nm in the output XML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cdtr/PstlAdr binding requires Z-fields (ZLISO/ZPFST/ZPLOR): hidden by default in FPAYHX layout. Without them populated, Cdtr address comes out empty or falls back to Dbtr-side fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>🧪 What this enables (Layer 3 of the 4-layer testing methodology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   This workbook delivers Layer 3 (DMEE Test Data with F110-history-replay-equivalent inputs) for the SEPA tree without requiring F110 execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 1 (Python simulator) = already done — 794 cases × 3 schemas = 2,382 PASS (claim 105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 2 (DMEE Test Data hand-crafted) = these 3 cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 3 (DMEE Test Data F110-history replay) = next iteration — pull actual REGUH/REGUP rows for top-15 scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 4 (D01 F110 integration) = Phase 3 final integration test</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   See companion BCM_StructuredAddressChange.html · Testing Simulation tab · 'Validation matrix alignment' for the full methodology.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="57">
     <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A41:L41"/>
     <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A46:L46"/>
     <mergeCell ref="A18:L18"/>
     <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A56:L56"/>
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A55:L55"/>
     <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A50:L50"/>
     <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A57:L57"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A42:L42"/>
     <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A47:L47"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A32:L32"/>
@@ -882,25 +1017,33 @@
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A53:L53"/>
     <mergeCell ref="A35:L35"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A20:L20"/>
     <mergeCell ref="A38:L38"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="A43:L43"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A44:L44"/>
     <mergeCell ref="A40:L40"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A39:L39"/>
     <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A48:L48"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A51:L51"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A45:L45"/>
     <mergeCell ref="A36:L36"/>
     <mergeCell ref="A6:L6"/>
   </mergeCells>
@@ -914,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -932,477 +1075,605 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Case 1 — Standard SEPA vendor payment (FR vendor, EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Scenario #1: SEPA-UNES-FR-EUR-S-O · 118,678 payments · 18.4% in-scope volume · Doc cat=01 (FI vendor invoice)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>📋 INSTRUCTIONS — Copy each table below into the matching grid in tx DMEE → /SEPA_CT_UNES → Display → Active version → Tree → Test (DMEE Test Data screen). The 'Row' column is just a counter for this Excel — do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>🔢 EXECUTION ORDER FOR THIS CASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>STEP 1 (V000 baseline) — tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>STEP 2 — In the popup, click 'Active version' button → tree opens in V000 view</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>STEP 3 — Menu: Tree → Test (or Test button on toolbar) → 'DMEE Test Data' screen opens with 3 empty grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>STEP 4 — Copy the FPAYHX row from this Excel into the FPAYHX grid (skip the 'Row' column — it is just an Excel counter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>STEP 5 — Copy the FPAYH row into the FPAYH grid (Doc cat. value is critical — use the value shown below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>STEP 6 — Copy the FPAYP row into the FPAYP grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>STEP 7 — (Optional but recommended) Expand FPAYHX layout: right-click header → Settings → add columns ZLISO, ZPFST, ZPLOR, ZSTRA — populate with values from the Z-FIELDS section below</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>STEP 8 — Click Test/Run button (typically green-checkmark icon or Execute) → SAP renders V000 XML in a new screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (or copy the full XML text into a text file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>STEP 10 (V001 comparison) — Press Back → return to DMEE Initial Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>STEP 11 — Display again → this time click 'Maintenance version' button → tree opens in V001 view</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>STEP 12 — Tree → Test → enter the EXACT SAME values from this Excel into the 3 grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>STEP 13 — Click Test/Run → SAP renders V001 XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>STEP 14 — Save the V001 XML as 'case_&lt;N&gt;_V001.xml'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>STEP 15 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml — V001 should show ADDITIONAL &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;; if those new tags appear with the same input → V001 design empirically validated for this case</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>📋 NOTES — The 'Row' column in each table below is an Excel counter, do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYHX — payment medium · formatting of payment data (Dbtr / UNESCO HQ side)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>PCd/city</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>POBox/str.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>ISO Code</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>IBAN at our House Bank</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>ISO</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>Reference number</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
+    <row r="24">
+      <c r="A24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>75007</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>7 PLACE DE FONTENOY</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>UNESCO</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>PARIS</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>SOG01</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>FR7630003000110000123456789</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>SOGEFRPP</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>TEST-V000-CASE1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYH — payment medium · data for payment (Cdtr / Payee side)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>No. FPAYHX</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Name of the payee</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>IBAN of the Payee</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Acct hold.</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Doc cat.</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>Ref. Doc.</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
+    <row r="28">
+      <c r="A28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>ACME SUPPLIES SARL</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>BNPAFRPPXXX</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>FR1420041010050500013M02606</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>ACME SUPPLIES SARL</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>5100012345</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>1500.00</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>01.04.2025</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYP — payment medium · data for paid items (line items)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>No. FPAYH</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Name (2)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
+    <row r="32">
+      <c r="A32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>Invoice 2025-001 services</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>ACME SUPPLIES SARL</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>🔶 Z-FIELDS (hidden by default — expand FPAYHX layout to populate)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Z-Field</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>Why this field</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>ZLISO</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>Cdtr country code (ISO) — for V000 Cdtr/PstlAdr/Ctry</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>ZPFST</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>15 RUE DE LA PAIX</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>Cdtr address line 1 — for V000 Cdtr/PstlAdr/AdrLine</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>ZPLOR</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>75002 PARIS</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Cdtr address line 2 — for V000 Cdtr/PstlAdr/AdrLine</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>ZSTRA</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>15 RUE DE LA PAIX</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>Cdtr street (for V001 StrtNm if testing V001 instead)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>📋 Expected XML output observations (V000)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="42" ht="35" customHeight="1">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Document/CstmrCdtTrfInitn/GrpHdr/InitgPty/Nm should reflect UNESCO (or SOG01 per current observed binding — flag for review)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="35" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="43" ht="35" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • PmtInf/Dbtr/Nm = UNESCO · /Dbtr/PstlAdr/Ctry = FR · /Dbtr/PstlAdr/AdrLine = PARIS (V000 Hybrid: Ctry + 1 AdrLine)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="35" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="44" ht="35" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • PmtInf/CdtTrfTxInf/Cdtr/Nm = ACME SUPPLIES SARL</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="35" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="45" ht="35" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • PmtInf/CdtTrfTxInf/Cdtr/PstlAdr — depends on Z-field bindings (ZLISO/ZPFST/ZPLOR); empty unless those are populated via expanded layout</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="35" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="46" ht="35" customHeight="1">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Amount: enter 1500.00 — observed 100x output (CtrlSum=150000.00) due to SEPA tree CV_RULE; expected behavior, not a bug for our purposes</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="70" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
+    <row r="48" ht="70" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
         <is>
           <t>🔄 V001 testing — after running V000 with the values above, switch to Maintenance version (Display → Maintenance version) and re-run with the SAME inputs. The V001 output should additionally have &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt; — fed from the Z-fields (ZSTRA/ZBSTR/etc.) byte-packed into FPAYHX-REF01..REF15 by Event 05. If V001 produces those structured tags with the same input → V001 design empirically validated against the SAP engine.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A24:L24"/>
+  <mergeCells count="30">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:L12"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A11:L11"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1414,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1432,485 +1703,613 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Case 2 — SEPA Payroll payment (employee, EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Scenario #2: SEPA-UNES-FR-EUR-S-P · 103,126 payments · 16% in-scope volume · Doc cat=03 (Payroll info)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>📋 INSTRUCTIONS — Copy each table below into the matching grid in tx DMEE → /SEPA_CT_UNES → Display → Active version → Tree → Test (DMEE Test Data screen). The 'Row' column is just a counter for this Excel — do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>🔢 EXECUTION ORDER FOR THIS CASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>STEP 1 (V000 baseline) — tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>STEP 2 — In the popup, click 'Active version' button → tree opens in V000 view</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>STEP 3 — Menu: Tree → Test (or Test button on toolbar) → 'DMEE Test Data' screen opens with 3 empty grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>STEP 4 — Copy the FPAYHX row from this Excel into the FPAYHX grid (skip the 'Row' column — it is just an Excel counter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>STEP 5 — Copy the FPAYH row into the FPAYH grid (Doc cat. value is critical — use the value shown below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>STEP 6 — Copy the FPAYP row into the FPAYP grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>STEP 7 — (Optional but recommended) Expand FPAYHX layout: right-click header → Settings → add columns ZLISO, ZPFST, ZPLOR, ZSTRA — populate with values from the Z-FIELDS section below</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>STEP 8 — Click Test/Run button (typically green-checkmark icon or Execute) → SAP renders V000 XML in a new screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (or copy the full XML text into a text file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>STEP 10 (V001 comparison) — Press Back → return to DMEE Initial Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>STEP 11 — Display again → this time click 'Maintenance version' button → tree opens in V001 view</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>STEP 12 — Tree → Test → enter the EXACT SAME values from this Excel into the 3 grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>STEP 13 — Click Test/Run → SAP renders V001 XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>STEP 14 — Save the V001 XML as 'case_&lt;N&gt;_V001.xml'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>STEP 15 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml — V001 should show ADDITIONAL &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;; if those new tags appear with the same input → V001 design empirically validated for this case</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>📋 NOTES — The 'Row' column in each table below is an Excel counter, do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYHX — payment medium · formatting of payment data (Dbtr / UNESCO HQ side)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>PCd/city</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>POBox/str.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>ISO Code</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>IBAN at our House Bank</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>ISO</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>Reference number</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
+    <row r="24">
+      <c r="A24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>75007</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>7 PLACE DE FONTENOY</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>UNESCO</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>PARIS</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>SOG01</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>FR7630003000110000123456789</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>SOGEFRPP</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>TEST-V000-PAYROLL-001</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYH — payment medium · data for payment (Cdtr / Payee side)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>No. FPAYHX</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Name of the payee</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>IBAN of the Payee</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Acct hold.</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Doc cat.</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>Ref. Doc.</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
+    <row r="28">
+      <c r="A28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>PIERRE MARTIN</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>BNPAFRPPXXX</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>FR7630002005500000987654321</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>PIERRE MARTIN</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>PR-2025-04-EMP12345</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>4500.00</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>30.04.2025</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYP — payment medium · data for paid items (line items)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>No. FPAYH</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Name (2)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
+    <row r="32">
+      <c r="A32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>April 2025 Salary</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>PIERRE MARTIN</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>🔶 Z-FIELDS (hidden by default — expand FPAYHX layout to populate)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Z-Field</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>Why this field</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>ZLISO</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>Employee country code (FR-resident employee)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>ZPFST</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>12 RUE DE RIVOLI</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>Employee residence street</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>ZPLOR</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>75001 PARIS</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Employee postal+city</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>ZSTRA</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>12 RUE DE RIVOLI</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>Employee street (V001 StrtNm if testing V001)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>📋 Expected XML output observations (V000)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="42" ht="35" customHeight="1">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Same Dbtr block as Case 1 (UNESCO HQ as payer)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="35" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="43" ht="35" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Doc cat=03 — Payroll category — this is what differentiates from Case 1</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="35" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="44" ht="35" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Cdtr is the employee, not a vendor — different name pattern (PIERRE MARTIN, fictional)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="35" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="45" ht="35" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Ref. Doc. follows Payroll naming pattern (PR-YYYY-MM-EMPID rather than 51000xxx invoice number)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="35" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="46" ht="35" customHeight="1">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Due date is end-of-month for payroll runs</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="35" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="47" ht="35" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Amount field semantics same as Case 1 (100x scaling at output)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="70" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+    <row r="49" ht="70" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
         <is>
           <t>🔄 V001 testing — after running V000 with the values above, switch to Maintenance version (Display → Maintenance version) and re-run with the SAME inputs. The V001 output should additionally have &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt; — fed from the Z-fields (ZSTRA/ZBSTR/etc.) byte-packed into FPAYHX-REF01..REF15 by Event 05. If V001 produces those structured tags with the same input → V001 design empirically validated against the SAP engine.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A24:L24"/>
+  <mergeCells count="31">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:L12"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A47:L47"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A49:L49"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1922,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1940,485 +2339,613 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Case 3 — SEPA cross-border vendor payment (ES vendor, EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>SEPA-zone non-FR creditor · tests how tree handles non-FR Cdtr country · Doc cat=01 (FI vendor invoice)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>📋 INSTRUCTIONS — Copy each table below into the matching grid in tx DMEE → /SEPA_CT_UNES → Display → Active version → Tree → Test (DMEE Test Data screen). The 'Row' column is just a counter for this Excel — do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>🔢 EXECUTION ORDER FOR THIS CASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>STEP 1 (V000 baseline) — tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>STEP 2 — In the popup, click 'Active version' button → tree opens in V000 view</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>STEP 3 — Menu: Tree → Test (or Test button on toolbar) → 'DMEE Test Data' screen opens with 3 empty grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>STEP 4 — Copy the FPAYHX row from this Excel into the FPAYHX grid (skip the 'Row' column — it is just an Excel counter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>STEP 5 — Copy the FPAYH row into the FPAYH grid (Doc cat. value is critical — use the value shown below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>STEP 6 — Copy the FPAYP row into the FPAYP grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>STEP 7 — (Optional but recommended) Expand FPAYHX layout: right-click header → Settings → add columns ZLISO, ZPFST, ZPLOR, ZSTRA — populate with values from the Z-FIELDS section below</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>STEP 8 — Click Test/Run button (typically green-checkmark icon or Execute) → SAP renders V000 XML in a new screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (or copy the full XML text into a text file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>STEP 10 (V001 comparison) — Press Back → return to DMEE Initial Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>STEP 11 — Display again → this time click 'Maintenance version' button → tree opens in V001 view</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>STEP 12 — Tree → Test → enter the EXACT SAME values from this Excel into the 3 grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>STEP 13 — Click Test/Run → SAP renders V001 XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>STEP 14 — Save the V001 XML as 'case_&lt;N&gt;_V001.xml'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>STEP 15 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml — V001 should show ADDITIONAL &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;; if those new tags appear with the same input → V001 design empirically validated for this case</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>📋 NOTES — The 'Row' column in each table below is an Excel counter, do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYHX — payment medium · formatting of payment data (Dbtr / UNESCO HQ side)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>PCd/city</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>POBox/str.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>ISO Code</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>IBAN at our House Bank</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>ISO</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>Reference number</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
+    <row r="24">
+      <c r="A24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>75007</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>7 PLACE DE FONTENOY</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>UNESCO</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>PARIS</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>SOG01</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>FR7630003000110000123456789</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>SOGEFRPP</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>TEST-V000-CROSSBORDER-001</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYH — payment medium · data for payment (Cdtr / Payee side)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>No. FPAYHX</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Name of the payee</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>IBAN of the Payee</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Acct hold.</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Doc cat.</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>Ref. Doc.</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
+    <row r="28">
+      <c r="A28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>BARCELONA SUPPLIES S.L.</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>BBVAESMMXXX</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>ES9121000418450200051332</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>BARCELONA SUPPLIES S.L.</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>5100099999</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>2750.00</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>15.04.2025</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYP — payment medium · data for paid items (line items)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>No. FPAYH</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Name (2)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
+    <row r="32">
+      <c r="A32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>Invoice 2025-Q2 IT services</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>BARCELONA SUPPLIES S.L.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>🔶 Z-FIELDS (hidden by default — expand FPAYHX layout to populate)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Z-Field</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>Why this field</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>ZLISO</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>Cdtr country code — Spain (verify this overrides Dbtr Ctr=FR in Cdtr block)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>ZPFST</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>GRAN VIA 235</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>Cdtr street (Spanish vendor address line 1)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>ZPLOR</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>08008 BARCELONA</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Cdtr postal+city</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>ZSTRA</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>GRAN VIA 235</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>Cdtr street (V001 StrtNm)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>📋 Expected XML output observations (V000)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="42" ht="35" customHeight="1">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Dbtr block identical to Cases 1+2 (UNESCO HQ)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="35" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="43" ht="35" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Cdtr country is ES (Spain) — verify Cdtr/PstlAdr/Ctry comes out as ES (not FR)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="35" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="44" ht="35" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • BIC differs (BBVAESMMXXX = BBVA Spain) — verify Cdtr/CdtrAgt/FinInstnId/BIC reflects this</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="35" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="45" ht="35" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • IBAN starts ES (Spanish IBAN format) — different from Cases 1+2 FR IBAN</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="35" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="46" ht="35" customHeight="1">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • This case validates that the SEPA tree correctly emits non-FR creditor data without Spain-specific bindings</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="35" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="47" ht="35" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • If output Cdtr country still says FR, it means the binding pulls from FPAYHX-Ctr (Dbtr) not from FPAYH or Z-fields — important V001 design implication</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="70" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+    <row r="49" ht="70" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
         <is>
           <t>🔄 V001 testing — after running V000 with the values above, switch to Maintenance version (Display → Maintenance version) and re-run with the SAME inputs. The V001 output should additionally have &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt; — fed from the Z-fields (ZSTRA/ZBSTR/etc.) byte-packed into FPAYHX-REF01..REF15 by Event 05. If V001 produces those structured tags with the same input → V001 design empirically validated against the SAP engine.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A24:L24"/>
+  <mergeCells count="31">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:L12"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A47:L47"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A49:L49"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Zagentexecution/incidents/xml_payment_structured_address/sepa_ct_unes_test_cases.xlsx
+++ b/Zagentexecution/incidents/xml_payment_structured_address/sepa_ct_unes_test_cases.xlsx
@@ -69,6 +69,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="000F172A"/>
       <sz val="12"/>
     </font>
@@ -77,12 +83,6 @@
       <b val="1"/>
       <color rgb="001f2937"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -792,203 +792,255 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>⚠ KEY CONSTRAINT discovered 2026-05-01 — tx DMEE only tests Active version</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>The 'Format tree → Test active version (F8)' menu in tx DMEE tests ONLY the Active version (the one with EX_STATUS='A'). There is no 'Test maintenance version' option in the standard menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Implication: each case in this workbook has TWO PHASES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Phase A — Test V000 (current production): runs anywhere (D01/V01/P01); F8 tests the production state directly. No risk to anything. This is the L1↔engine equivalence proof for the simulator V000 predictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Phase B — Test V001 (proposed design): MUST be done in D01 ONLY because V001 testing requires activation, which OVERWRITES V000 in the system where activation runs. Procedure: (a) Generate Version snapshot of D01 V000 to V002 [rollback enabler], (b) Activate V001 in D01 [V001 content becomes the new V000 in D01], (c) F8 Test active version in D01 [now testing what was V001], (d) save the XML, (e) ROLLBACK by retrieving V002 from Version Management → Activate [original D01 V000 restored].</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   NEVER do Phase B in P01. P01 stays on V000 production behaviour throughout Phase 3 testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Each case tab below has the explicit STEP-by-STEP procedure for both phases (17 steps total per case = 9 for V000 + 6 for V001 activation/test/rollback in D01 + 2 for diff).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
           <t>📋 General workbook navigation</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Each case tab is self-contained — has the EXECUTION ORDER (15 steps) at the top + the 3 tables to copy + the Z-fields hint + expected XML observations + V001 testing reminder.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Skip the 'Row' column from each table in the Excel — it is just a counter for the worksheet, not a SAP field.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Keep 'No. FPAYHX' = 1 and 'No. FPAYH' = 1 for a single-payment test.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>For Cdtr address to render: expand the FPAYHX grid layout to add Z-fields (ZLISO, ZPFST, ZPLOR, ZSTRA, ZBSTR…) — see each case's Z-FIELDS section.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>📊 The 3 cases — coverage rationale</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Case 1 — Standard SEPA vendor payment (FR vendor, EUR)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Scenario #1 — 118,678 payments — 18.4% volume — Doc cat=01 (FI vendor invoice)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   The most common scenario. Validates baseline V000 SEPA output and provides the V001 reference for diff.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Case 2 — SEPA Payroll (employee, EUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Scenario #2 — 103,126 payments — 16% volume — Doc cat=03 (Payroll info)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Same tree, different document category. Validates that Doc cat=03 routes through the same SEPA chain without breaking format.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Case 3 — SEPA cross-border to ES vendor (Spanish vendor, EUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SEPA-zone non-FR creditor — Doc cat=01 (FI vendor invoice)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tests that non-FR Cdtr country is correctly emitted (Cdtr/PstlAdr/Ctry=ES). Surfaces if the tree falls back to Dbtr country.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>⚠ Known SEPA tree behaviors (from initial V000 test session 2026-05-01)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Amount × 100 at output: Amount=1500.00 in FPAYH produces CtrlSum=150000.00 in XML. Expected SEPA tree CV_RULE — production-correct.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • InitgPty/Nm = SOG01 (HBKID): bound to FPAYHX-Issuer field, not to UNESCO name. Flag for review with N_MENARD if business intent is 'UNESCO' rather than HBKID.</t>
+          <t xml:space="preserve">   Scenario #2 — 103,126 payments — 16% volume — Doc cat=03 (Payroll info)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • UltmtCdtr/Nm bound to FPAYP-NAME1: when FPAYP 'Name' is populated, it appears as UltmtCdtr/Nm in the output XML.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Cdtr/PstlAdr binding requires Z-fields (ZLISO/ZPFST/ZPLOR): hidden by default in FPAYHX layout. Without them populated, Cdtr address comes out empty or falls back to Dbtr-side fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>🧪 What this enables (Layer 3 of the 4-layer testing methodology)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   This workbook delivers Layer 3 (DMEE Test Data with F110-history-replay-equivalent inputs) for the SEPA tree without requiring F110 execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Layer 1 (Python simulator) = already done — 794 cases × 3 schemas = 2,382 PASS (claim 105)</t>
+          <t xml:space="preserve">   Same tree, different document category. Validates that Doc cat=03 routes through the same SEPA chain without breaking format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Case 3 — SEPA cross-border to ES vendor (Spanish vendor, EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SEPA-zone non-FR creditor — Doc cat=01 (FI vendor invoice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tests that non-FR Cdtr country is correctly emitted (Cdtr/PstlAdr/Ctry=ES). Surfaces if the tree falls back to Dbtr country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>⚠ Known SEPA tree behaviors (from initial V000 test session 2026-05-01)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Layer 2 (DMEE Test Data hand-crafted) = these 3 cases</t>
+          <t xml:space="preserve">   • Amount × 100 at output: Amount=1500.00 in FPAYH produces CtrlSum=150000.00 in XML. Expected SEPA tree CV_RULE — production-correct.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Layer 3 (DMEE Test Data F110-history replay) = next iteration — pull actual REGUH/REGUP rows for top-15 scenarios</t>
+          <t xml:space="preserve">   • InitgPty/Nm = SOG01 (HBKID): bound to FPAYHX-Issuer field, not to UNESCO name. Flag for review with N_MENARD if business intent is 'UNESCO' rather than HBKID.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Layer 4 (D01 F110 integration) = Phase 3 final integration test</t>
+          <t xml:space="preserve">   • UltmtCdtr/Nm bound to FPAYP-NAME1: when FPAYP 'Name' is populated, it appears as UltmtCdtr/Nm in the output XML.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   • Cdtr/PstlAdr binding requires Z-fields (ZLISO/ZPFST/ZPLOR): hidden by default in FPAYHX layout. Without them populated, Cdtr address comes out empty or falls back to Dbtr-side fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>🧪 What this enables (Layer 3 of the 4-layer testing methodology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   This workbook delivers Layer 3 (DMEE Test Data with F110-history-replay-equivalent inputs) for the SEPA tree without requiring F110 execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 1 (Python simulator) = already done — 794 cases × 3 schemas = 2,382 PASS (claim 105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 2 (DMEE Test Data hand-crafted) = these 3 cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 3 (DMEE Test Data F110-history replay) = next iteration — pull actual REGUH/REGUP rows for top-15 scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Layer 4 (D01 F110 integration) = Phase 3 final integration test</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   See companion BCM_StructuredAddressChange.html · Testing Simulation tab · 'Validation matrix alignment' for the full methodology.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="65">
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A54:L54"/>
     <mergeCell ref="A7:L7"/>
@@ -1020,6 +1072,7 @@
     <mergeCell ref="A53:L53"/>
     <mergeCell ref="A35:L35"/>
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A62:L62"/>
     <mergeCell ref="A20:L20"/>
     <mergeCell ref="A38:L38"/>
     <mergeCell ref="A29:L29"/>
@@ -1027,25 +1080,32 @@
     <mergeCell ref="A52:L52"/>
     <mergeCell ref="A43:L43"/>
     <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A63:L63"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A58:L58"/>
     <mergeCell ref="A40:L40"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A39:L39"/>
     <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A59:L59"/>
     <mergeCell ref="A48:L48"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A60:L60"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A49:L49"/>
     <mergeCell ref="A51:L51"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
     <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A61:L61"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A65:L65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1057,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1098,582 +1158,642 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>STEP 1 (V000 baseline) — tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
+          <t>⚠ KEY CONSTRAINT — tx DMEE menu only exposes 'Format tree → Test active version' (F8). It tests ONLY whichever version has EX_STATUS='A'. To test V001 with the SAP engine, V001 MUST be activated first (which makes V001's content the new V000 per SAP-correct lifecycle in version-concept tab). The V001 test is therefore done in D01 with snapshot+activate+test+rollback procedure — NOT in P01.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>STEP 2 — In the popup, click 'Active version' button → tree opens in V000 view</t>
-        </is>
-      </c>
+      <c r="A5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>STEP 3 — Menu: Tree → Test (or Test button on toolbar) → 'DMEE Test Data' screen opens with 3 empty grids</t>
+          <t>═══ PHASE A · Test V000 (current production behaviour) ═══</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>STEP 4 — Copy the FPAYHX row from this Excel into the FPAYHX grid (skip the 'Row' column — it is just an Excel counter)</t>
+          <t>STEP 1 — Open tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>STEP 5 — Copy the FPAYH row into the FPAYH grid (Doc cat. value is critical — use the value shown below)</t>
+          <t>STEP 2 — In popup, click 'Active version' → tree opens in V000</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>STEP 6 — Copy the FPAYP row into the FPAYP grid</t>
+          <t>STEP 3 — Menu: Format tree → Test active version (F8) → 'DMEE Test Data' screen opens</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>STEP 7 — (Optional but recommended) Expand FPAYHX layout: right-click header → Settings → add columns ZLISO, ZPFST, ZPLOR, ZSTRA — populate with values from the Z-FIELDS section below</t>
+          <t>STEP 4 — Copy FPAYHX row from this Excel (skip 'Row' column) → FPAYHX grid</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>STEP 8 — Click Test/Run button (typically green-checkmark icon or Execute) → SAP renders V000 XML in a new screen</t>
+          <t>STEP 5 — Copy FPAYH row → FPAYH grid (Doc cat. value matters: 01 vs 03)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (or copy the full XML text into a text file)</t>
+          <t>STEP 6 — Copy FPAYP row → FPAYP grid</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>STEP 10 (V001 comparison) — Press Back → return to DMEE Initial Screen</t>
+          <t>STEP 7 — Optional: expand FPAYHX layout to add Z-fields (ZLISO, ZPFST, ZPLOR, ZSTRA) — see Z-FIELDS section below. Without them, Cdtr/PstlAdr renders empty.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>STEP 11 — Display again → this time click 'Maintenance version' button → tree opens in V001 view</t>
+          <t>STEP 8 — Click Test/Run → SAP renders V000 XML output</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>STEP 12 — Tree → Test → enter the EXACT SAME values from this Excel into the 3 grids</t>
+          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (copy text or use Download XML file)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>STEP 13 — Click Test/Run → SAP renders V001 XML</t>
-        </is>
-      </c>
+      <c r="A16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>STEP 14 — Save the V001 XML as 'case_&lt;N&gt;_V001.xml'</t>
+          <t>═══ PHASE B · Test V001 (proposed design) — D01 ONLY, with snapshot+rollback safety ═══</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>STEP 15 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml — V001 should show ADDITIONAL &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;; if those new tags appear with the same input → V001 design empirically validated for this case</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+          <t>STEP 10 (D01 PRE-FLIGHT) — Confirm you are in D01 (NOT P01). V001 testing must NEVER be done in P01 because activation = overwrite of V000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>STEP 11 (SNAPSHOT FOR ROLLBACK) — In D01: tx DMEE → /SEPA_CT_UNES → Display → Maintenance version → Format tree → Change → Utilities → Versions → Generate Version → SAP archives current D01 V000 to V002 (or next free number). Note the version number assigned. THIS IS THE ROLLBACK ENABLER — do not skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>STEP 12 (BUILD V001 IF NOT YET DONE) — In Change mode on V001, apply the matrix-row INSERTs/MODIFY/SYNC for the V001 design. Save → captures workbench transport (R3TR DMEE class K).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>STEP 13 (ACTIVATE V001) — Tree → Activate (or button on Change-mode toolbar). SAP runs consistency check; if clean, V001 content is stored as V000 (overwrites the previous V000 — but it's safely archived in V002 from STEP 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>STEP 14 (TEST THE NEW V000 = V001 CONTENT) — Repeat STEPS 1-9 above in D01. The 'Active version' is now what V001 used to be. The output XML is the V001 engine output for this input. Save as 'case_&lt;N&gt;_V001.xml'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>STEP 15 (ROLLBACK D01 TO ORIGINAL V000) — Tree → Versions → Version Management → select V002 → Retrieve → V002 content copies into V001 → Activate → original V000 content restored as Active. D01 is now back to the pre-test state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>═══ PHASE C · Diff and validate ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>STEP 16 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml. V001 should show ADDITIONAL &lt;StrtNm&gt;/&lt;BldgNb&gt;/&lt;PstCd&gt;/&lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;. If those new tags appear with the same input → V001 design empirically validated against the SAP engine for this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>STEP 17 — Compare both outputs against the Python simulator's predictions (Layer 1) for the same input. If V000 engine ≡ V000 simulator AND V001 engine ≡ V001 simulator → claim 105 (simulator correctness-equivalence) empirically proven for this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>📋 NOTES — The 'Row' column in each table below is an Excel counter, do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYHX — payment medium · formatting of payment data (Dbtr / UNESCO HQ side)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>PCd/city</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>POBox/str.</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>ISO Code</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>IBAN at our House Bank</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>ISO</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>Reference number</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
+    <row r="33">
+      <c r="A33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>75007</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>7 PLACE DE FONTENOY</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>UNESCO</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>PARIS</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>SOG01</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>FR7630003000110000123456789</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J33" s="18" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="K33" s="18" t="inlineStr">
         <is>
           <t>SOGEFRPP</t>
         </is>
       </c>
-      <c r="L24" s="18" t="inlineStr">
+      <c r="L33" s="18" t="inlineStr">
         <is>
           <t>TEST-V000-CASE1</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYH — payment medium · data for payment (Cdtr / Payee side)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>No. FPAYHX</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Name of the payee</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>IBAN of the Payee</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>Acct hold.</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Doc cat.</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>Ref. Doc.</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="n">
+    <row r="37">
+      <c r="A37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>ACME SUPPLIES SARL</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>BNPAFRPPXXX</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>FR1420041010050500013M02606</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>ACME SUPPLIES SARL</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>5100012345</t>
         </is>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>1500.00</t>
         </is>
       </c>
-      <c r="J28" s="18" t="inlineStr">
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>01.04.2025</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYP — payment medium · data for paid items (line items)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>No. FPAYH</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>Name (2)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="n">
+    <row r="41">
+      <c r="A41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Invoice 2025-001 services</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>ACME SUPPLIES SARL</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>🔶 Z-FIELDS (hidden by default — expand FPAYHX layout to populate)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Z-Field</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>Why this field</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>ZLISO</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>Cdtr country code (ISO) — for V000 Cdtr/PstlAdr/Ctry</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>ZPFST</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>15 RUE DE LA PAIX</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>Cdtr address line 1 — for V000 Cdtr/PstlAdr/AdrLine</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>ZPLOR</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>75002 PARIS</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>Cdtr address line 2 — for V000 Cdtr/PstlAdr/AdrLine</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>ZSTRA</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>15 RUE DE LA PAIX</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>Cdtr street (for V001 StrtNm if testing V001 instead)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>📋 Expected XML output observations (V000)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="35" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+    <row r="51" ht="35" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Document/CstmrCdtTrfInitn/GrpHdr/InitgPty/Nm should reflect UNESCO (or SOG01 per current observed binding — flag for review)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="35" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+    <row r="52" ht="35" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • PmtInf/Dbtr/Nm = UNESCO · /Dbtr/PstlAdr/Ctry = FR · /Dbtr/PstlAdr/AdrLine = PARIS (V000 Hybrid: Ctry + 1 AdrLine)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="35" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
+    <row r="53" ht="35" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • PmtInf/CdtTrfTxInf/Cdtr/Nm = ACME SUPPLIES SARL</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="35" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
+    <row r="54" ht="35" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • PmtInf/CdtTrfTxInf/Cdtr/PstlAdr — depends on Z-field bindings (ZLISO/ZPFST/ZPLOR); empty unless those are populated via expanded layout</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="35" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="55" ht="35" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Amount: enter 1500.00 — observed 100x output (CtrlSum=150000.00) due to SEPA tree CV_RULE; expected behavior, not a bug for our purposes</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="70" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
+    <row r="57" ht="70" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>🔄 V001 testing — after running V000 with the values above, switch to Maintenance version (Display → Maintenance version) and re-run with the SAME inputs. The V001 output should additionally have &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt; — fed from the Z-fields (ZSTRA/ZBSTR/etc.) byte-packed into FPAYHX-REF01..REF15 by Event 05. If V001 produces those structured tags with the same input → V001 design empirically validated against the SAP engine.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="39">
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A55:L55"/>
     <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A57:L57"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A53:L53"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A29:L29"/>
     <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A31:L31"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A51:L51"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A45:L45"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1685,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1726,590 +1846,650 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>STEP 1 (V000 baseline) — tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
+          <t>⚠ KEY CONSTRAINT — tx DMEE menu only exposes 'Format tree → Test active version' (F8). It tests ONLY whichever version has EX_STATUS='A'. To test V001 with the SAP engine, V001 MUST be activated first (which makes V001's content the new V000 per SAP-correct lifecycle in version-concept tab). The V001 test is therefore done in D01 with snapshot+activate+test+rollback procedure — NOT in P01.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>STEP 2 — In the popup, click 'Active version' button → tree opens in V000 view</t>
-        </is>
-      </c>
+      <c r="A5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>STEP 3 — Menu: Tree → Test (or Test button on toolbar) → 'DMEE Test Data' screen opens with 3 empty grids</t>
+          <t>═══ PHASE A · Test V000 (current production behaviour) ═══</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>STEP 4 — Copy the FPAYHX row from this Excel into the FPAYHX grid (skip the 'Row' column — it is just an Excel counter)</t>
+          <t>STEP 1 — Open tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>STEP 5 — Copy the FPAYH row into the FPAYH grid (Doc cat. value is critical — use the value shown below)</t>
+          <t>STEP 2 — In popup, click 'Active version' → tree opens in V000</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>STEP 6 — Copy the FPAYP row into the FPAYP grid</t>
+          <t>STEP 3 — Menu: Format tree → Test active version (F8) → 'DMEE Test Data' screen opens</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>STEP 7 — (Optional but recommended) Expand FPAYHX layout: right-click header → Settings → add columns ZLISO, ZPFST, ZPLOR, ZSTRA — populate with values from the Z-FIELDS section below</t>
+          <t>STEP 4 — Copy FPAYHX row from this Excel (skip 'Row' column) → FPAYHX grid</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>STEP 8 — Click Test/Run button (typically green-checkmark icon or Execute) → SAP renders V000 XML in a new screen</t>
+          <t>STEP 5 — Copy FPAYH row → FPAYH grid (Doc cat. value matters: 01 vs 03)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (or copy the full XML text into a text file)</t>
+          <t>STEP 6 — Copy FPAYP row → FPAYP grid</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>STEP 10 (V001 comparison) — Press Back → return to DMEE Initial Screen</t>
+          <t>STEP 7 — Optional: expand FPAYHX layout to add Z-fields (ZLISO, ZPFST, ZPLOR, ZSTRA) — see Z-FIELDS section below. Without them, Cdtr/PstlAdr renders empty.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>STEP 11 — Display again → this time click 'Maintenance version' button → tree opens in V001 view</t>
+          <t>STEP 8 — Click Test/Run → SAP renders V000 XML output</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>STEP 12 — Tree → Test → enter the EXACT SAME values from this Excel into the 3 grids</t>
+          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (copy text or use Download XML file)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>STEP 13 — Click Test/Run → SAP renders V001 XML</t>
-        </is>
-      </c>
+      <c r="A16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>STEP 14 — Save the V001 XML as 'case_&lt;N&gt;_V001.xml'</t>
+          <t>═══ PHASE B · Test V001 (proposed design) — D01 ONLY, with snapshot+rollback safety ═══</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>STEP 15 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml — V001 should show ADDITIONAL &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;; if those new tags appear with the same input → V001 design empirically validated for this case</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+          <t>STEP 10 (D01 PRE-FLIGHT) — Confirm you are in D01 (NOT P01). V001 testing must NEVER be done in P01 because activation = overwrite of V000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>STEP 11 (SNAPSHOT FOR ROLLBACK) — In D01: tx DMEE → /SEPA_CT_UNES → Display → Maintenance version → Format tree → Change → Utilities → Versions → Generate Version → SAP archives current D01 V000 to V002 (or next free number). Note the version number assigned. THIS IS THE ROLLBACK ENABLER — do not skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>STEP 12 (BUILD V001 IF NOT YET DONE) — In Change mode on V001, apply the matrix-row INSERTs/MODIFY/SYNC for the V001 design. Save → captures workbench transport (R3TR DMEE class K).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>STEP 13 (ACTIVATE V001) — Tree → Activate (or button on Change-mode toolbar). SAP runs consistency check; if clean, V001 content is stored as V000 (overwrites the previous V000 — but it's safely archived in V002 from STEP 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>STEP 14 (TEST THE NEW V000 = V001 CONTENT) — Repeat STEPS 1-9 above in D01. The 'Active version' is now what V001 used to be. The output XML is the V001 engine output for this input. Save as 'case_&lt;N&gt;_V001.xml'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>STEP 15 (ROLLBACK D01 TO ORIGINAL V000) — Tree → Versions → Version Management → select V002 → Retrieve → V002 content copies into V001 → Activate → original V000 content restored as Active. D01 is now back to the pre-test state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>═══ PHASE C · Diff and validate ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>STEP 16 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml. V001 should show ADDITIONAL &lt;StrtNm&gt;/&lt;BldgNb&gt;/&lt;PstCd&gt;/&lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;. If those new tags appear with the same input → V001 design empirically validated against the SAP engine for this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>STEP 17 — Compare both outputs against the Python simulator's predictions (Layer 1) for the same input. If V000 engine ≡ V000 simulator AND V001 engine ≡ V001 simulator → claim 105 (simulator correctness-equivalence) empirically proven for this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>📋 NOTES — The 'Row' column in each table below is an Excel counter, do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYHX — payment medium · formatting of payment data (Dbtr / UNESCO HQ side)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>PCd/city</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>POBox/str.</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>ISO Code</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>IBAN at our House Bank</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>ISO</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>Reference number</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
+    <row r="33">
+      <c r="A33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>75007</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>7 PLACE DE FONTENOY</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>UNESCO</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>PARIS</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>SOG01</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>FR7630003000110000123456789</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J33" s="18" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="K33" s="18" t="inlineStr">
         <is>
           <t>SOGEFRPP</t>
         </is>
       </c>
-      <c r="L24" s="18" t="inlineStr">
+      <c r="L33" s="18" t="inlineStr">
         <is>
           <t>TEST-V000-PAYROLL-001</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYH — payment medium · data for payment (Cdtr / Payee side)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>No. FPAYHX</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Name of the payee</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>IBAN of the Payee</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>Acct hold.</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Doc cat.</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>Ref. Doc.</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="n">
+    <row r="37">
+      <c r="A37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>PIERRE MARTIN</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>BNPAFRPPXXX</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>FR7630002005500000987654321</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>PIERRE MARTIN</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>PR-2025-04-EMP12345</t>
         </is>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>4500.00</t>
         </is>
       </c>
-      <c r="J28" s="18" t="inlineStr">
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>30.04.2025</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYP — payment medium · data for paid items (line items)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>No. FPAYH</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>Name (2)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="n">
+    <row r="41">
+      <c r="A41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>April 2025 Salary</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>PIERRE MARTIN</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>🔶 Z-FIELDS (hidden by default — expand FPAYHX layout to populate)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Z-Field</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>Why this field</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>ZLISO</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>Employee country code (FR-resident employee)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>ZPFST</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>12 RUE DE RIVOLI</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>Employee residence street</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>ZPLOR</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>75001 PARIS</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>Employee postal+city</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>ZSTRA</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>12 RUE DE RIVOLI</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>Employee street (V001 StrtNm if testing V001)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>📋 Expected XML output observations (V000)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="35" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+    <row r="51" ht="35" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Same Dbtr block as Case 1 (UNESCO HQ as payer)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="35" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+    <row r="52" ht="35" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Doc cat=03 — Payroll category — this is what differentiates from Case 1</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="35" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
+    <row r="53" ht="35" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Cdtr is the employee, not a vendor — different name pattern (PIERRE MARTIN, fictional)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="35" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
+    <row r="54" ht="35" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Ref. Doc. follows Payroll naming pattern (PR-YYYY-MM-EMPID rather than 51000xxx invoice number)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="35" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="55" ht="35" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Due date is end-of-month for payroll runs</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="35" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+    <row r="56" ht="35" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Amount field semantics same as Case 1 (100x scaling at output)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="70" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
+    <row r="58" ht="70" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>🔄 V001 testing — after running V000 with the values above, switch to Maintenance version (Display → Maintenance version) and re-run with the SAME inputs. The V001 output should additionally have &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt; — fed from the Z-fields (ZSTRA/ZBSTR/etc.) byte-packed into FPAYHX-REF01..REF15 by Event 05. If V001 produces those structured tags with the same input → V001 design empirically validated against the SAP engine.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="40">
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A56:L56"/>
     <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A55:L55"/>
     <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A47:L47"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A53:L53"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A29:L29"/>
     <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A58:L58"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A51:L51"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A45:L45"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2321,7 +2501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2362,590 +2542,650 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>STEP 1 (V000 baseline) — tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
+          <t>⚠ KEY CONSTRAINT — tx DMEE menu only exposes 'Format tree → Test active version' (F8). It tests ONLY whichever version has EX_STATUS='A'. To test V001 with the SAP engine, V001 MUST be activated first (which makes V001's content the new V000 per SAP-correct lifecycle in version-concept tab). The V001 test is therefore done in D01 with snapshot+activate+test+rollback procedure — NOT in P01.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>STEP 2 — In the popup, click 'Active version' button → tree opens in V000 view</t>
-        </is>
-      </c>
+      <c r="A5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>STEP 3 — Menu: Tree → Test (or Test button on toolbar) → 'DMEE Test Data' screen opens with 3 empty grids</t>
+          <t>═══ PHASE A · Test V000 (current production behaviour) ═══</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>STEP 4 — Copy the FPAYHX row from this Excel into the FPAYHX grid (skip the 'Row' column — it is just an Excel counter)</t>
+          <t>STEP 1 — Open tx DMEE → Tree type=PAYM + Format tree=/SEPA_CT_UNES → click Display</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>STEP 5 — Copy the FPAYH row into the FPAYH grid (Doc cat. value is critical — use the value shown below)</t>
+          <t>STEP 2 — In popup, click 'Active version' → tree opens in V000</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>STEP 6 — Copy the FPAYP row into the FPAYP grid</t>
+          <t>STEP 3 — Menu: Format tree → Test active version (F8) → 'DMEE Test Data' screen opens</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>STEP 7 — (Optional but recommended) Expand FPAYHX layout: right-click header → Settings → add columns ZLISO, ZPFST, ZPLOR, ZSTRA — populate with values from the Z-FIELDS section below</t>
+          <t>STEP 4 — Copy FPAYHX row from this Excel (skip 'Row' column) → FPAYHX grid</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>STEP 8 — Click Test/Run button (typically green-checkmark icon or Execute) → SAP renders V000 XML in a new screen</t>
+          <t>STEP 5 — Copy FPAYH row → FPAYH grid (Doc cat. value matters: 01 vs 03)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (or copy the full XML text into a text file)</t>
+          <t>STEP 6 — Copy FPAYP row → FPAYP grid</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>STEP 10 (V001 comparison) — Press Back → return to DMEE Initial Screen</t>
+          <t>STEP 7 — Optional: expand FPAYHX layout to add Z-fields (ZLISO, ZPFST, ZPLOR, ZSTRA) — see Z-FIELDS section below. Without them, Cdtr/PstlAdr renders empty.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>STEP 11 — Display again → this time click 'Maintenance version' button → tree opens in V001 view</t>
+          <t>STEP 8 — Click Test/Run → SAP renders V000 XML output</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>STEP 12 — Tree → Test → enter the EXACT SAME values from this Excel into the 3 grids</t>
+          <t>STEP 9 — Save the V000 XML as 'case_&lt;N&gt;_V000.xml' (copy text or use Download XML file)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>STEP 13 — Click Test/Run → SAP renders V001 XML</t>
-        </is>
-      </c>
+      <c r="A16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>STEP 14 — Save the V001 XML as 'case_&lt;N&gt;_V001.xml'</t>
+          <t>═══ PHASE B · Test V001 (proposed design) — D01 ONLY, with snapshot+rollback safety ═══</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>STEP 15 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml — V001 should show ADDITIONAL &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;; if those new tags appear with the same input → V001 design empirically validated for this case</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+          <t>STEP 10 (D01 PRE-FLIGHT) — Confirm you are in D01 (NOT P01). V001 testing must NEVER be done in P01 because activation = overwrite of V000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>STEP 11 (SNAPSHOT FOR ROLLBACK) — In D01: tx DMEE → /SEPA_CT_UNES → Display → Maintenance version → Format tree → Change → Utilities → Versions → Generate Version → SAP archives current D01 V000 to V002 (or next free number). Note the version number assigned. THIS IS THE ROLLBACK ENABLER — do not skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>STEP 12 (BUILD V001 IF NOT YET DONE) — In Change mode on V001, apply the matrix-row INSERTs/MODIFY/SYNC for the V001 design. Save → captures workbench transport (R3TR DMEE class K).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>STEP 13 (ACTIVATE V001) — Tree → Activate (or button on Change-mode toolbar). SAP runs consistency check; if clean, V001 content is stored as V000 (overwrites the previous V000 — but it's safely archived in V002 from STEP 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>STEP 14 (TEST THE NEW V000 = V001 CONTENT) — Repeat STEPS 1-9 above in D01. The 'Active version' is now what V001 used to be. The output XML is the V001 engine output for this input. Save as 'case_&lt;N&gt;_V001.xml'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>STEP 15 (ROLLBACK D01 TO ORIGINAL V000) — Tree → Versions → Version Management → select V002 → Retrieve → V002 content copies into V001 → Activate → original V000 content restored as Active. D01 is now back to the pre-test state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>═══ PHASE C · Diff and validate ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>STEP 16 — Diff case_&lt;N&gt;_V000.xml vs case_&lt;N&gt;_V001.xml. V001 should show ADDITIONAL &lt;StrtNm&gt;/&lt;BldgNb&gt;/&lt;PstCd&gt;/&lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt;. If those new tags appear with the same input → V001 design empirically validated against the SAP engine for this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>STEP 17 — Compare both outputs against the Python simulator's predictions (Layer 1) for the same input. If V000 engine ≡ V000 simulator AND V001 engine ≡ V001 simulator → claim 105 (simulator correctness-equivalence) empirically proven for this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>📋 NOTES — The 'Row' column in each table below is an Excel counter, do NOT enter it in SAP. Headers match SAP screen labels exactly. The 'No. FPAYHX' / 'No. FPAYH' columns are foreign keys linking the 3 tables — keep them = 1 for a single-payment test.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYHX — payment medium · formatting of payment data (Dbtr / UNESCO HQ side)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>PCd/city</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>POBox/str.</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>ISO Code</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>IBAN at our House Bank</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>ISO</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>Reference number</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
+    <row r="33">
+      <c r="A33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>75007</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>7 PLACE DE FONTENOY</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>UNESCO</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>PARIS</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>SOG01</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>FR7630003000110000123456789</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J33" s="18" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="K33" s="18" t="inlineStr">
         <is>
           <t>SOGEFRPP</t>
         </is>
       </c>
-      <c r="L24" s="18" t="inlineStr">
+      <c r="L33" s="18" t="inlineStr">
         <is>
           <t>TEST-V000-CROSSBORDER-001</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYH — payment medium · data for payment (Cdtr / Payee side)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>No. FPAYHX</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Name of the payee</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>SWIFT/BIC</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>IBAN of the Payee</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>Acct hold.</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Doc cat.</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>Ref. Doc.</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="n">
+    <row r="37">
+      <c r="A37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>BARCELONA SUPPLIES S.L.</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>BBVAESMMXXX</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>ES9121000418450200051332</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>BARCELONA SUPPLIES S.L.</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>5100099999</t>
         </is>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>2750.00</t>
         </is>
       </c>
-      <c r="J28" s="18" t="inlineStr">
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>15.04.2025</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>🟢 FPAYP — payment medium · data for paid items (line items)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>No. FPAYH</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Ctr</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>Name (2)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="n">
+    <row r="41">
+      <c r="A41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Invoice 2025-Q2 IT services</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>BARCELONA SUPPLIES S.L.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>🔶 Z-FIELDS (hidden by default — expand FPAYHX layout to populate)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Z-Field</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>Why this field</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>ZLISO</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>Cdtr country code — Spain (verify this overrides Dbtr Ctr=FR in Cdtr block)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>ZPFST</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>GRAN VIA 235</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>Cdtr street (Spanish vendor address line 1)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>ZPLOR</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>08008 BARCELONA</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>Cdtr postal+city</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>ZSTRA</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>GRAN VIA 235</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>Cdtr street (V001 StrtNm)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>📋 Expected XML output observations (V000)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="35" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+    <row r="51" ht="35" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Dbtr block identical to Cases 1+2 (UNESCO HQ)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="35" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+    <row r="52" ht="35" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Cdtr country is ES (Spain) — verify Cdtr/PstlAdr/Ctry comes out as ES (not FR)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="35" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
+    <row r="53" ht="35" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • BIC differs (BBVAESMMXXX = BBVA Spain) — verify Cdtr/CdtrAgt/FinInstnId/BIC reflects this</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="35" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
+    <row r="54" ht="35" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • IBAN starts ES (Spanish IBAN format) — different from Cases 1+2 FR IBAN</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="35" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="55" ht="35" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • This case validates that the SEPA tree correctly emits non-FR creditor data without Spain-specific bindings</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="35" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+    <row r="56" ht="35" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  • If output Cdtr country still says FR, it means the binding pulls from FPAYHX-Ctr (Dbtr) not from FPAYH or Z-fields — important V001 design implication</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="70" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
+    <row r="58" ht="70" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>🔄 V001 testing — after running V000 with the values above, switch to Maintenance version (Display → Maintenance version) and re-run with the SAME inputs. The V001 output should additionally have &lt;StrtNm&gt;, &lt;BldgNb&gt;, &lt;PstCd&gt;, &lt;TwnNm&gt; tags inside &lt;Cdtr&gt;&lt;PstlAdr&gt; and &lt;Dbtr&gt;&lt;PstlAdr&gt; — fed from the Z-fields (ZSTRA/ZBSTR/etc.) byte-packed into FPAYHX-REF01..REF15 by Event 05. If V001 produces those structured tags with the same input → V001 design empirically validated against the SAP engine.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="40">
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A56:L56"/>
     <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A55:L55"/>
     <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A47:L47"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A53:L53"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A29:L29"/>
     <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A58:L58"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A51:L51"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A45:L45"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
